--- a/InputFiles/Bento/TC14_Bento_arm-a_FileType-text.xlsx
+++ b/InputFiles/Bento/TC14_Bento_arm-a_FileType-text.xlsx
@@ -537,12 +537,13 @@
 MATCH (ss)&lt;-[*..2]-(parent)&lt;--(f:file)
 WHERE f.file_type = 'text'
 OPTIONAL MATCH (f)-[*]-&gt;(samp:sample)
+OPTIONAL MATCH (f)-[:file_of_laboratory_procedure]-&gt;(lp:laboratory_procedure)
 RETURN
   count(DISTINCT p.program_id) AS Programs,
   count(DISTINCT s.study_acronym) AS Arms,
   count(DISTINCT ss.study_subject_id) AS Cases,
   count(DISTINCT samp.sample_id) AS Samples,
-  count(DISTINCT f.file_id) AS Assays,
+  count(DISTINCT lp.laboratory_procedure_id) AS Assays,
   count(DISTINCT f.file_id) AS Files</t>
         </is>
       </c>
